--- a/data/dw_table.xlsx
+++ b/data/dw_table.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{885ACF5A-98E1-C345-AFCF-8728D8689BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C305E93-A49C-8A4B-AED5-8DDDD79E31E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16100" xr2:uid="{E9F1DA6A-4FAA-5143-B6A8-F5EB0E9CBCC4}"/>
+    <workbookView xWindow="-36540" yWindow="-1940" windowWidth="28100" windowHeight="16800" xr2:uid="{E9F1DA6A-4FAA-5143-B6A8-F5EB0E9CBCC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -487,13 +487,13 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>5.26328E-2</v>
+        <v>6.5090841675777597E-2</v>
       </c>
       <c r="C3">
-        <v>4.0236090000000002E-2</v>
+        <v>5.1087502395413965E-2</v>
       </c>
       <c r="D3">
-        <v>6.4560800000000002E-2</v>
+        <v>7.9345105734142371E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -501,13 +501,13 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>6.7587919999999996E-2</v>
+        <v>6.8931613131132288E-2</v>
       </c>
       <c r="C4">
-        <v>5.1647459999999999E-2</v>
+        <v>5.1841354883477367E-2</v>
       </c>
       <c r="D4">
-        <v>8.3670999999999995E-2</v>
+        <v>8.721015688680446E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -515,13 +515,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>5.5841160000000001E-2</v>
+        <v>5.5841162763935519E-2</v>
       </c>
       <c r="C5">
-        <v>4.4179169999999997E-2</v>
+        <v>4.4179170194543448E-2</v>
       </c>
       <c r="D5">
-        <v>6.4480319999999994E-2</v>
+        <v>6.4480320921935189E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -529,13 +529,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>6.8068169999999997E-2</v>
+        <v>6.8950211774975873E-2</v>
       </c>
       <c r="C6">
-        <v>5.0411400000000002E-2</v>
+        <v>5.1312027011335852E-2</v>
       </c>
       <c r="D6">
-        <v>8.5339129999999999E-2</v>
+        <v>8.7540296396625333E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -543,13 +543,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0.1518996</v>
+        <v>0.20722720143266157</v>
       </c>
       <c r="C7">
-        <v>0.12505369999999999</v>
+        <v>0.16617673188559229</v>
       </c>
       <c r="D7">
-        <v>0.17587520000000001</v>
+        <v>0.2360096614537957</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -557,13 +557,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>0.16934200999999999</v>
+        <v>0.16934200918895112</v>
       </c>
       <c r="C8">
-        <v>0.10475464</v>
+        <v>0.10475464189657885</v>
       </c>
       <c r="D8">
-        <v>0.25876628000000002</v>
+        <v>0.25876628163526788</v>
       </c>
     </row>
   </sheetData>

--- a/data/dw_table.xlsx
+++ b/data/dw_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C305E93-A49C-8A4B-AED5-8DDDD79E31E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A92E97-ECB1-CB4D-AB12-63F1CB335CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36540" yWindow="-1940" windowWidth="28100" windowHeight="16800" xr2:uid="{E9F1DA6A-4FAA-5143-B6A8-F5EB0E9CBCC4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{E9F1DA6A-4FAA-5143-B6A8-F5EB0E9CBCC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>disease</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>dw_up</t>
-  </si>
-  <si>
-    <t>bc</t>
   </si>
   <si>
     <t>mort</t>
@@ -448,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{519CA767-6689-624E-9CDE-DF2ADA6EFFE7}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="16.1640625" customWidth="1"/>
@@ -470,7 +467,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -484,7 +481,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>6.5090841675777597E-2</v>
@@ -498,16 +495,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>6.8931613131132288E-2</v>
+        <v>5.5841162763935519E-2</v>
       </c>
       <c r="C4">
-        <v>5.1841354883477367E-2</v>
+        <v>4.4179170194543448E-2</v>
       </c>
       <c r="D4">
-        <v>8.721015688680446E-2</v>
+        <v>6.4480320921935189E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -515,13 +512,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>5.5841162763935519E-2</v>
+        <v>6.8950211774975873E-2</v>
       </c>
       <c r="C5">
-        <v>4.4179170194543448E-2</v>
+        <v>5.1312027011335852E-2</v>
       </c>
       <c r="D5">
-        <v>6.4480320921935189E-2</v>
+        <v>8.7540296396625333E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -529,13 +526,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>6.8950211774975873E-2</v>
+        <v>0.20722720143266157</v>
       </c>
       <c r="C6">
-        <v>5.1312027011335852E-2</v>
+        <v>0.16617673188559229</v>
       </c>
       <c r="D6">
-        <v>8.7540296396625333E-2</v>
+        <v>0.2360096614537957</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -543,26 +540,12 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0.20722720143266157</v>
+        <v>0.16934200918895112</v>
       </c>
       <c r="C7">
-        <v>0.16617673188559229</v>
+        <v>0.10475464189657885</v>
       </c>
       <c r="D7">
-        <v>0.2360096614537957</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>0.16934200918895112</v>
-      </c>
-      <c r="C8">
-        <v>0.10475464189657885</v>
-      </c>
-      <c r="D8">
         <v>0.25876628163526788</v>
       </c>
     </row>

--- a/data/dw_table.xlsx
+++ b/data/dw_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A92E97-ECB1-CB4D-AB12-63F1CB335CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD330247-526F-204B-AAFD-3B777DA49CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{E9F1DA6A-4FAA-5143-B6A8-F5EB0E9CBCC4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>disease</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>dep</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>cc</t>
   </si>
 </sst>
 </file>
@@ -445,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{519CA767-6689-624E-9CDE-DF2ADA6EFFE7}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="16.1640625" customWidth="1"/>
@@ -481,71 +487,99 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>6.5090841675777597E-2</v>
+        <v>6.8895146412577088E-2</v>
       </c>
       <c r="C3">
-        <v>5.1087502395413965E-2</v>
+        <v>5.2608280646638535E-2</v>
       </c>
       <c r="D3">
-        <v>7.9345105734142371E-2</v>
+        <v>8.7937005811260793E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>5.5841162763935519E-2</v>
+        <v>8.9368477539454663E-2</v>
       </c>
       <c r="C4">
-        <v>4.4179170194543448E-2</v>
+        <v>7.1361693094938311E-2</v>
       </c>
       <c r="D4">
-        <v>6.4480320921935189E-2</v>
+        <v>0.1039047586920917</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>6.8950211774975873E-2</v>
+        <v>6.5090841675777597E-2</v>
       </c>
       <c r="C5">
-        <v>5.1312027011335852E-2</v>
+        <v>5.1087502395413965E-2</v>
       </c>
       <c r="D5">
-        <v>8.7540296396625333E-2</v>
+        <v>7.9345105734142371E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>0.20722720143266157</v>
+        <v>5.5841162763935519E-2</v>
       </c>
       <c r="C6">
-        <v>0.16617673188559229</v>
+        <v>4.4179170194543448E-2</v>
       </c>
       <c r="D6">
-        <v>0.2360096614537957</v>
+        <v>6.4480320921935189E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>6.8950211774975873E-2</v>
+      </c>
+      <c r="C7">
+        <v>5.1312027011335852E-2</v>
+      </c>
+      <c r="D7">
+        <v>8.7540296396625333E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>0.20722720143266157</v>
+      </c>
+      <c r="C8">
+        <v>0.16617673188559229</v>
+      </c>
+      <c r="D8">
+        <v>0.2360096614537957</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B9">
         <v>0.16934200918895112</v>
       </c>
-      <c r="C7">
+      <c r="C9">
         <v>0.10475464189657885</v>
       </c>
-      <c r="D7">
+      <c r="D9">
         <v>0.25876628163526788</v>
       </c>
     </row>

--- a/data/dw_table.xlsx
+++ b/data/dw_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD330247-526F-204B-AAFD-3B777DA49CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B736A13-7FA0-034D-8218-7AAC1F6EBAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{E9F1DA6A-4FAA-5143-B6A8-F5EB0E9CBCC4}"/>
+    <workbookView xWindow="0" yWindow="7940" windowWidth="28800" windowHeight="8660" xr2:uid="{E9F1DA6A-4FAA-5143-B6A8-F5EB0E9CBCC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
